--- a/capacity/dist/2027-Capacity-Example-RiskGroup.xlsx
+++ b/capacity/dist/2027-Capacity-Example-RiskGroup.xlsx
@@ -26,36 +26,37 @@
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'5. Capacity asks'!$5:$5</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'5. Capacity asks'!$A$5:$T$305</definedName>
     <definedName function="false" hidden="false" name="AskNatureList" vbProcedure="false">Ref!$I$56:$I$58</definedName>
-    <definedName function="false" hidden="false" name="AttritionDefault" vbProcedure="false">Ref!$B$8</definedName>
+    <definedName function="false" hidden="false" name="AttritionDefault" vbProcedure="false">Ref!$B$7</definedName>
     <definedName function="false" hidden="false" name="BaseYear" vbProcedure="false">Ref!$B$6</definedName>
+    <definedName function="false" hidden="false" name="CategoryList" vbProcedure="false">Ref!$O$56:$O$61</definedName>
     <definedName function="false" hidden="false" name="CostEnvelope" vbProcedure="false">Ref!$B$17</definedName>
     <definedName function="false" hidden="false" name="DriverCategory" vbProcedure="false">Ref!$B$35:$B$53</definedName>
     <definedName function="false" hidden="false" name="DriverList" vbProcedure="false">Ref!$A$35:$A$53</definedName>
     <definedName function="false" hidden="false" name="DriverRank" vbProcedure="false">Ref!$C$35:$C$53</definedName>
-    <definedName function="false" hidden="false" name="GosiOther" vbProcedure="false">Ref!$B$12</definedName>
-    <definedName function="false" hidden="false" name="GosiSaudi" vbProcedure="false">Ref!$B$11</definedName>
+    <definedName function="false" hidden="false" name="GosiOther" vbProcedure="false">Ref!$B$11</definedName>
+    <definedName function="false" hidden="false" name="GosiSaudi" vbProcedure="false">Ref!$B$10</definedName>
     <definedName function="false" hidden="false" name="GradeBasic" vbProcedure="false">Ref!$B$23:$B$31</definedName>
     <definedName function="false" hidden="false" name="GradeBonus" vbProcedure="false">Ref!$E$23:$E$31</definedName>
     <definedName function="false" hidden="false" name="GradeHousing" vbProcedure="false">Ref!$C$23:$C$31</definedName>
     <definedName function="false" hidden="false" name="GradeList" vbProcedure="false">Ref!$A$23:$A$31</definedName>
     <definedName function="false" hidden="false" name="GradeRank" vbProcedure="false">Ref!$F$23:$F$31</definedName>
     <definedName function="false" hidden="false" name="GradeTransport" vbProcedure="false">Ref!$D$23:$D$31</definedName>
-    <definedName function="false" hidden="false" name="GroupName" vbProcedure="false">Ref!$B$7</definedName>
+    <definedName function="false" hidden="false" name="GroupName" vbProcedure="false">Ref!$B$14</definedName>
     <definedName function="false" hidden="false" name="HeadEnvelope" vbProcedure="false">Ref!$B$18</definedName>
     <definedName function="false" hidden="false" name="LadderLevels" vbProcedure="false">Ref!$M$56:$M$61</definedName>
-    <definedName function="false" hidden="false" name="OneOffJunior" vbProcedure="false">Ref!$B$13</definedName>
-    <definedName function="false" hidden="false" name="OneOffSenior" vbProcedure="false">Ref!$B$14</definedName>
+    <definedName function="false" hidden="false" name="OneOffJunior" vbProcedure="false">Ref!$B$12</definedName>
+    <definedName function="false" hidden="false" name="OneOffSenior" vbProcedure="false">Ref!$B$13</definedName>
     <definedName function="false" hidden="false" name="PlanYear" vbProcedure="false">Ref!$B$5</definedName>
-    <definedName function="false" hidden="false" name="ProductivityDefault" vbProcedure="false">Ref!$B$9</definedName>
+    <definedName function="false" hidden="false" name="ProductivityDefault" vbProcedure="false">Ref!$B$8</definedName>
     <definedName function="false" hidden="false" name="QuarterList" vbProcedure="false">Ref!$C$56:$C$59</definedName>
-    <definedName function="false" hidden="false" name="SalaryInflation" vbProcedure="false">Ref!$B$10</definedName>
+    <definedName function="false" hidden="false" name="SalaryInflation" vbProcedure="false">Ref!$B$9</definedName>
     <definedName function="false" hidden="false" name="SaudiBasisList" vbProcedure="false">Ref!$G$56:$G$58</definedName>
     <definedName function="false" hidden="false" name="SaudiTarget" vbProcedure="false">Ref!$B$19</definedName>
     <definedName function="false" hidden="false" name="StructureActions" vbProcedure="false">Ref!$K$56:$K$60</definedName>
-    <definedName function="false" hidden="false" name="UnitList" vbProcedure="false">Ref!$Q$56:$Q$123</definedName>
+    <definedName function="false" hidden="false" name="UnitList" vbProcedure="false">Ref!$S$56:$S$123</definedName>
     <definedName function="false" hidden="false" name="WorkforceTypes" vbProcedure="false">Ref!$E$56:$E$58</definedName>
     <definedName function="false" hidden="false" name="WorkloadDrivers" vbProcedure="false">Ref!$A$56:$A$70</definedName>
-    <definedName function="false" hidden="false" name="YesNo" vbProcedure="false">Ref!$O$56:$O$57</definedName>
+    <definedName function="false" hidden="false" name="YesNo" vbProcedure="false">Ref!$Q$56:$Q$57</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="632">
   <si>
     <t xml:space="preserve">2027 Capacity Exercise</t>
   </si>
@@ -1797,10 +1798,10 @@
     <t xml:space="preserve">Employer GOSI - non-Saudi</t>
   </si>
   <si>
-    <t xml:space="preserve">One-off cost - grade below G14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-off cost - grade G14 and above</t>
+    <t xml:space="preserve">One-off cost - below G14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-off cost - G14 and above</t>
   </si>
   <si>
     <t xml:space="preserve">Envelope for this group</t>
@@ -2776,13 +2777,13 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61377934"/>
-        <c:axId val="11651292"/>
+        <c:axId val="84382355"/>
+        <c:axId val="69967875"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61377934"/>
+        <c:axId val="84382355"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2812,7 +2813,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11651292"/>
+        <c:crossAx val="69967875"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2820,7 +2821,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11651292"/>
+        <c:axId val="69967875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2862,8 +2863,8 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61377934"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="84382355"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -3016,11 +3017,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="86721592"/>
-        <c:axId val="36616772"/>
+        <c:axId val="18604110"/>
+        <c:axId val="9309542"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86721592"/>
+        <c:axId val="18604110"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3052,7 +3053,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36616772"/>
+        <c:crossAx val="9309542"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3060,7 +3061,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36616772"/>
+        <c:axId val="9309542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3102,7 +3103,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86721592"/>
+        <c:crossAx val="18604110"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -26228,7 +26229,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q123"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -26280,66 +26281,66 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>38</v>
+        <v>571</v>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B8" s="55" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B9" s="55" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B10" s="55" t="n">
-        <v>0.04</v>
+        <v>0.1175</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B11" s="55" t="n">
-        <v>0.1175</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="B12" s="55" t="n">
-        <v>0.02</v>
+        <v>576</v>
+      </c>
+      <c r="B12" s="56" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B13" s="56" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="B14" s="56" t="n">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26424,7 +26425,7 @@
       <c r="E23" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26444,7 +26445,7 @@
       <c r="E24" s="57" t="n">
         <v>0.06</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26464,7 +26465,7 @@
       <c r="E25" s="57" t="n">
         <v>0.08</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26484,7 +26485,7 @@
       <c r="E26" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26504,7 +26505,7 @@
       <c r="E27" s="57" t="n">
         <v>0.12</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -26524,7 +26525,7 @@
       <c r="E28" s="57" t="n">
         <v>0.15</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -26544,7 +26545,7 @@
       <c r="E29" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -26564,7 +26565,7 @@
       <c r="E30" s="57" t="n">
         <v>0.25</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="21" t="n">
         <v>8</v>
       </c>
     </row>
@@ -26584,7 +26585,7 @@
       <c r="E31" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="21" t="n">
         <v>9</v>
       </c>
     </row>
@@ -26836,9 +26837,12 @@
         <v>612</v>
       </c>
       <c r="O55" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q55" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="Q55" s="6" t="s">
+      <c r="S55" s="6" t="s">
         <v>494</v>
       </c>
     </row>
@@ -26865,9 +26869,12 @@
         <v>37</v>
       </c>
       <c r="O56" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q56" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="Q56" s="0" t="s">
+      <c r="S56" s="0" t="s">
         <v>38</v>
       </c>
     </row>
@@ -26894,9 +26901,12 @@
         <v>39</v>
       </c>
       <c r="O57" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q57" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="Q57" s="0" t="s">
+      <c r="S57" s="0" t="s">
         <v>309</v>
       </c>
     </row>
@@ -26922,7 +26932,10 @@
       <c r="M58" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="Q58" s="0" t="s">
+      <c r="O58" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="S58" s="0" t="s">
         <v>123</v>
       </c>
     </row>
@@ -26939,7 +26952,10 @@
       <c r="M59" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="Q59" s="0" t="s">
+      <c r="O59" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="S59" s="0" t="s">
         <v>125</v>
       </c>
     </row>
@@ -26953,7 +26969,10 @@
       <c r="M60" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="Q60" s="0" t="s">
+      <c r="O60" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="S60" s="0" t="s">
         <v>618</v>
       </c>
     </row>
@@ -26964,7 +26983,10 @@
       <c r="M61" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="Q61" s="0" t="s">
+      <c r="O61" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="S61" s="0" t="s">
         <v>395</v>
       </c>
     </row>
@@ -26972,7 +26994,7 @@
       <c r="A62" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="Q62" s="0" t="s">
+      <c r="S62" s="0" t="s">
         <v>126</v>
       </c>
     </row>
@@ -26980,7 +27002,7 @@
       <c r="A63" s="0" t="s">
         <v>507</v>
       </c>
-      <c r="Q63" s="0" t="s">
+      <c r="S63" s="0" t="s">
         <v>245</v>
       </c>
     </row>
@@ -26988,7 +27010,7 @@
       <c r="A64" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="Q64" s="0" t="s">
+      <c r="S64" s="0" t="s">
         <v>221</v>
       </c>
     </row>
@@ -26996,7 +27018,7 @@
       <c r="A65" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="Q65" s="0" t="s">
+      <c r="S65" s="0" t="s">
         <v>128</v>
       </c>
     </row>
@@ -27004,7 +27026,7 @@
       <c r="A66" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="Q66" s="0" t="s">
+      <c r="S66" s="0" t="s">
         <v>130</v>
       </c>
     </row>
@@ -27012,7 +27034,7 @@
       <c r="A67" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="Q67" s="0" t="s">
+      <c r="S67" s="0" t="s">
         <v>224</v>
       </c>
     </row>
@@ -27020,7 +27042,7 @@
       <c r="A68" s="0" t="s">
         <v>514</v>
       </c>
-      <c r="Q68" s="0" t="s">
+      <c r="S68" s="0" t="s">
         <v>249</v>
       </c>
     </row>
@@ -27028,7 +27050,7 @@
       <c r="A69" s="0" t="s">
         <v>516</v>
       </c>
-      <c r="Q69" s="0" t="s">
+      <c r="S69" s="0" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27036,272 +27058,272 @@
       <c r="A70" s="0" t="s">
         <v>518</v>
       </c>
-      <c r="Q70" s="0" t="s">
+      <c r="S70" s="0" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q71" s="0" t="s">
+      <c r="S71" s="0" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q72" s="0" t="s">
+      <c r="S72" s="0" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q73" s="0" t="s">
+      <c r="S73" s="0" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q74" s="0" t="s">
+      <c r="S74" s="0" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q75" s="0" t="s">
+      <c r="S75" s="0" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q76" s="0" t="s">
+      <c r="S76" s="0" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q77" s="0" t="s">
+      <c r="S77" s="0" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q78" s="0" t="s">
+      <c r="S78" s="0" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q79" s="0" t="s">
+      <c r="S79" s="0" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q80" s="0" t="s">
+      <c r="S80" s="0" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q81" s="0" t="s">
+      <c r="S81" s="0" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q82" s="0" t="s">
+      <c r="S82" s="0" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q83" s="0" t="s">
+      <c r="S83" s="0" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q84" s="0" t="s">
+      <c r="S84" s="0" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q85" s="0" t="s">
+      <c r="S85" s="0" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q86" s="0" t="s">
+      <c r="S86" s="0" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q87" s="0" t="s">
+      <c r="S87" s="0" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q88" s="0" t="s">
+      <c r="S88" s="0" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q89" s="0" t="s">
+      <c r="S89" s="0" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q90" s="0" t="s">
+      <c r="S90" s="0" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q91" s="0" t="s">
+      <c r="S91" s="0" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q92" s="0" t="s">
+      <c r="S92" s="0" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q93" s="0" t="s">
+      <c r="S93" s="0" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q94" s="0" t="s">
+      <c r="S94" s="0" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q95" s="0" t="s">
+      <c r="S95" s="0" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q96" s="0" t="s">
+      <c r="S96" s="0" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q97" s="0" t="s">
+      <c r="S97" s="0" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q98" s="0" t="s">
+      <c r="S98" s="0" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q99" s="0" t="s">
+      <c r="S99" s="0" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q100" s="0" t="s">
+      <c r="S100" s="0" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q101" s="0" t="s">
+      <c r="S101" s="0" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q102" s="0" t="s">
+      <c r="S102" s="0" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q103" s="0" t="s">
+      <c r="S103" s="0" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q104" s="0" t="s">
+      <c r="S104" s="0" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q105" s="0" t="s">
+      <c r="S105" s="0" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q106" s="0" t="s">
+      <c r="S106" s="0" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q107" s="0" t="s">
+      <c r="S107" s="0" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q108" s="0" t="s">
+      <c r="S108" s="0" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q109" s="0" t="s">
+      <c r="S109" s="0" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q110" s="0" t="s">
+      <c r="S110" s="0" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q111" s="0" t="s">
+      <c r="S111" s="0" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q112" s="0" t="s">
+      <c r="S112" s="0" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q113" s="0" t="s">
+      <c r="S113" s="0" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q114" s="0" t="s">
+      <c r="S114" s="0" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q115" s="0" t="s">
+      <c r="S115" s="0" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q116" s="0" t="s">
+      <c r="S116" s="0" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q117" s="0" t="s">
+      <c r="S117" s="0" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q118" s="0" t="s">
+      <c r="S118" s="0" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q119" s="0" t="s">
+      <c r="S119" s="0" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q120" s="0" t="s">
+      <c r="S120" s="0" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q121" s="0" t="s">
+      <c r="S121" s="0" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q122" s="0" t="s">
+      <c r="S122" s="0" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q123" s="0" t="s">
+      <c r="S123" s="0" t="s">
         <v>194</v>
       </c>
     </row>
